--- a/Extracted_data_analysis/global/Output-Transformed_data/sampling_unit_tot.xlsx
+++ b/Extracted_data_analysis/global/Output-Transformed_data/sampling_unit_tot.xlsx
@@ -440,7 +440,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
@@ -451,7 +451,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4">
@@ -462,7 +462,7 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
@@ -473,7 +473,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
